--- a/Bugs.xlsx
+++ b/Bugs.xlsx
@@ -67,16 +67,16 @@
     <t>BUG-TC12</t>
   </si>
   <si>
-    <t>Открытие страницы News</t>
-  </si>
-  <si>
-    <t>Добавление новости</t>
-  </si>
-  <si>
-    <t>Совместимость приложения Хоспис с темами ОС</t>
-  </si>
-  <si>
-    <t>Локализация приложения</t>
+    <t>Новости не отображаются на странице News при открытии меню</t>
+  </si>
+  <si>
+    <t>Новая новость не появляется в списке при добавлении через Control panel</t>
+  </si>
+  <si>
+    <t>Некорректное отображение интерфейса в приложении Хоспис при смене темы устройства</t>
+  </si>
+  <si>
+    <t>Некорректная локализация приложения при смене языка устройства</t>
   </si>
   <si>
     <t>Major</t>
